--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-seltene-empfehlung-evidenzgraduierung.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-seltene-empfehlung-evidenzgraduierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:39:17+00:00</t>
+    <t>2026-08-28T13:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-seltene-empfehlung-evidenzgraduierung.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-seltene-empfehlung-evidenzgraduierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:49:20+00:00</t>
+    <t>2026-08-28T14:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-seltene-empfehlung-evidenzgraduierung.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-seltene-empfehlung-evidenzgraduierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:00:29+00:00</t>
+    <t>2026-08-31T13:41:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
